--- a/data/trans_orig/imc_inf-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/imc_inf-Estudios-trans_orig.xlsx
@@ -526,7 +526,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Índice de masa corporal (IMC) medio de los menores, declarado por los/as progenitores/as</t>
+          <t>Índice de masa corporal (IMC) medio de los menores, declarado por los/as progenitores/as (tasa de respuesta: 87,47%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -716,62 +716,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>18,44; 20,24</t>
+          <t>18,5; 20,3</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>18,69; 20,58</t>
+          <t>18,77; 20,65</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>19,8; 23,04</t>
+          <t>19,89; 23,29</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>17,59; 20,29</t>
+          <t>17,5; 20,34</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>19,79; 23,13</t>
+          <t>19,76; 22,95</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>19,05; 20,58</t>
+          <t>19,02; 20,68</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>18,94; 21,02</t>
+          <t>18,92; 21,03</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>18,4; 24,73</t>
+          <t>18,29; 23,44</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>19,35; 21,3</t>
+          <t>19,34; 21,0</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>19,18; 20,37</t>
+          <t>19,09; 20,34</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>19,61; 21,51</t>
+          <t>19,63; 21,6</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>18,38; 20,93</t>
+          <t>18,42; 21,3</t>
         </is>
       </c>
     </row>
@@ -856,62 +856,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>18,8; 19,5</t>
+          <t>18,79; 19,51</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>19,05; 19,86</t>
+          <t>19,06; 19,89</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>18,27; 18,92</t>
+          <t>18,28; 18,92</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>18,72; 20,3</t>
+          <t>18,75; 20,22</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>19,34; 20,09</t>
+          <t>19,33; 20,12</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>19,8; 21,16</t>
+          <t>19,73; 21,09</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>18,68; 19,54</t>
+          <t>18,69; 19,59</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>19,33; 20,37</t>
+          <t>19,3; 20,34</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>19,17; 19,69</t>
+          <t>19,18; 19,69</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>19,54; 20,38</t>
+          <t>19,53; 20,38</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>18,61; 19,13</t>
+          <t>18,59; 19,13</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>19,17; 19,99</t>
+          <t>19,15; 20,04</t>
         </is>
       </c>
     </row>
@@ -996,62 +996,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>18,1; 19,19</t>
+          <t>18,1; 19,32</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>18,01; 19,25</t>
+          <t>18,08; 19,28</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>18,03; 19,56</t>
+          <t>17,99; 19,5</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>17,41; 18,71</t>
+          <t>17,49; 18,68</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>18,69; 20,98</t>
+          <t>18,62; 20,93</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>18,43; 19,63</t>
+          <t>18,46; 19,66</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>18,21; 19,74</t>
+          <t>18,29; 19,69</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>17,41; 18,3</t>
+          <t>17,39; 18,31</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>18,47; 19,73</t>
+          <t>18,5; 19,78</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>18,41; 19,23</t>
+          <t>18,39; 19,22</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>18,32; 19,41</t>
+          <t>18,35; 19,37</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>17,57; 18,36</t>
+          <t>17,57; 18,29</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1136,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>18,75; 19,3</t>
+          <t>18,76; 19,34</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>18,99; 19,62</t>
+          <t>18,99; 19,63</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>18,55; 19,16</t>
+          <t>18,54; 19,17</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>18,54; 19,63</t>
+          <t>18,56; 19,74</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>19,45; 20,22</t>
+          <t>19,4; 20,19</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>19,58; 20,55</t>
+          <t>19,55; 20,5</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>18,8; 19,51</t>
+          <t>18,79; 19,51</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>18,95; 19,79</t>
+          <t>18,9; 19,75</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>19,18; 19,68</t>
+          <t>19,19; 19,68</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>19,37; 19,95</t>
+          <t>19,35; 19,95</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>18,73; 19,2</t>
+          <t>18,74; 19,2</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>18,84; 19,54</t>
+          <t>18,87; 19,52</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/imc_inf-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/imc_inf-Estudios-trans_orig.xlsx
@@ -716,62 +716,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>18,5; 20,3</t>
+          <t>18,54; 20,29</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>18,77; 20,65</t>
+          <t>18,73; 20,58</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>19,89; 23,29</t>
+          <t>20,01; 23,41</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>17,5; 20,34</t>
+          <t>17,6; 20,29</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>19,76; 22,95</t>
+          <t>19,76; 23,42</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>19,02; 20,68</t>
+          <t>19,18; 20,73</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>18,92; 21,03</t>
+          <t>18,98; 20,97</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>18,29; 23,44</t>
+          <t>18,32; 23,59</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>19,34; 21,0</t>
+          <t>19,34; 21,14</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>19,09; 20,34</t>
+          <t>19,09; 20,36</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>19,63; 21,6</t>
+          <t>19,69; 21,5</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>18,42; 21,3</t>
+          <t>18,51; 21,36</t>
         </is>
       </c>
     </row>
@@ -856,62 +856,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>18,79; 19,51</t>
+          <t>18,79; 19,44</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>19,06; 19,89</t>
+          <t>19,08; 19,9</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>18,28; 18,92</t>
+          <t>18,3; 18,88</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>18,75; 20,22</t>
+          <t>18,8; 20,33</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>19,33; 20,12</t>
+          <t>19,34; 20,12</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>19,73; 21,09</t>
+          <t>19,78; 21,13</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>18,69; 19,59</t>
+          <t>18,67; 19,56</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>19,3; 20,34</t>
+          <t>19,3; 20,31</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>19,18; 19,69</t>
+          <t>19,2; 19,72</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>19,53; 20,38</t>
+          <t>19,59; 20,37</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>18,59; 19,13</t>
+          <t>18,6; 19,14</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>19,15; 20,04</t>
+          <t>19,19; 20,04</t>
         </is>
       </c>
     </row>
@@ -996,62 +996,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>18,1; 19,32</t>
+          <t>18,03; 19,21</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>18,08; 19,28</t>
+          <t>18,09; 19,23</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>17,99; 19,5</t>
+          <t>18,03; 19,62</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>17,49; 18,68</t>
+          <t>17,46; 18,63</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>18,62; 20,93</t>
+          <t>18,6; 21,03</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>18,46; 19,66</t>
+          <t>18,44; 19,67</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>18,29; 19,69</t>
+          <t>18,25; 19,63</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>17,39; 18,31</t>
+          <t>17,39; 18,27</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>18,5; 19,78</t>
+          <t>18,47; 19,66</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>18,39; 19,22</t>
+          <t>18,42; 19,28</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>18,35; 19,37</t>
+          <t>18,29; 19,33</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>17,57; 18,29</t>
+          <t>17,57; 18,3</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1136,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>18,76; 19,34</t>
+          <t>18,72; 19,28</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>18,99; 19,63</t>
+          <t>18,97; 19,64</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>18,54; 19,17</t>
+          <t>18,53; 19,14</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>18,56; 19,74</t>
+          <t>18,56; 19,67</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>19,4; 20,19</t>
+          <t>19,46; 20,24</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>19,55; 20,5</t>
+          <t>19,56; 20,54</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>18,79; 19,51</t>
+          <t>18,75; 19,46</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>18,9; 19,75</t>
+          <t>18,94; 19,78</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>19,19; 19,68</t>
+          <t>19,18; 19,66</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>19,35; 19,95</t>
+          <t>19,38; 19,97</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>18,74; 19,2</t>
+          <t>18,73; 19,21</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>18,87; 19,52</t>
+          <t>18,89; 19,55</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/imc_inf-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/imc_inf-Estudios-trans_orig.xlsx
@@ -532,7 +532,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -540,7 +540,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -648,42 +648,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>20,87</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>19,83</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>19,88</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>19,98</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>19,26</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>19,62</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>21,14</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>19,13</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>20,87</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>19,83</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>19,88</t>
-        </is>
-      </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>19,69</t>
+          <t>19,67</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -703,7 +703,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>19,43</t>
+          <t>19,84</t>
         </is>
       </c>
     </row>
@@ -716,62 +716,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>18,54; 20,29</t>
+          <t>19,79; 23,13</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>18,73; 20,58</t>
+          <t>19,05; 20,58</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>20,01; 23,41</t>
+          <t>18,94; 21,02</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>17,6; 20,29</t>
+          <t>18,56; 24,98</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>19,76; 23,42</t>
+          <t>18,44; 20,24</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>19,18; 20,73</t>
+          <t>18,69; 20,58</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>18,98; 20,97</t>
+          <t>19,8; 23,04</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>18,32; 23,59</t>
+          <t>18,73; 20,69</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>19,34; 21,14</t>
+          <t>19,35; 21,3</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>19,09; 20,36</t>
+          <t>19,18; 20,37</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>19,69; 21,5</t>
+          <t>19,61; 21,51</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>18,51; 21,36</t>
+          <t>18,94; 21,71</t>
         </is>
       </c>
     </row>
@@ -788,42 +788,42 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>19,69</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>20,33</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>19,09</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>19,83</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
           <t>19,14</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>19,47</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>18,59</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>19,28</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>19,69</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>20,33</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>19,09</t>
-        </is>
-      </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>19,74</t>
+          <t>19,01</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -843,7 +843,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>19,53</t>
+          <t>19,45</t>
         </is>
       </c>
     </row>
@@ -856,62 +856,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>18,79; 19,44</t>
+          <t>19,34; 20,09</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>19,08; 19,9</t>
+          <t>19,8; 21,16</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>18,3; 18,88</t>
+          <t>18,68; 19,54</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>18,8; 20,33</t>
+          <t>19,43; 20,42</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>19,34; 20,12</t>
+          <t>18,8; 19,5</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>19,78; 21,13</t>
+          <t>19,05; 19,86</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>18,67; 19,56</t>
+          <t>18,27; 18,92</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>19,3; 20,31</t>
+          <t>18,63; 19,5</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>19,2; 19,72</t>
+          <t>19,17; 19,69</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>19,59; 20,37</t>
+          <t>19,54; 20,38</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>18,6; 19,14</t>
+          <t>18,61; 19,13</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>19,19; 20,04</t>
+          <t>19,13; 19,82</t>
         </is>
       </c>
     </row>
@@ -928,42 +928,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>19,51</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>18,97</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>18,86</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>17,91</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>18,56</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>18,61</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>18,65</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>17,98</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>19,51</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>18,97</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>18,86</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>17,83</t>
+          <t>18,0</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>17,9</t>
+          <t>17,95</t>
         </is>
       </c>
     </row>
@@ -996,62 +996,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>18,03; 19,21</t>
+          <t>18,69; 20,98</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>18,09; 19,23</t>
+          <t>18,43; 19,63</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>18,03; 19,62</t>
+          <t>18,21; 19,74</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>17,46; 18,63</t>
+          <t>17,48; 18,38</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>18,6; 21,03</t>
+          <t>18,1; 19,19</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>18,44; 19,67</t>
+          <t>18,01; 19,25</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>18,25; 19,63</t>
+          <t>18,03; 19,56</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>17,39; 18,27</t>
+          <t>17,42; 18,73</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>18,47; 19,66</t>
+          <t>18,47; 19,73</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>18,42; 19,28</t>
+          <t>18,41; 19,23</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>18,29; 19,33</t>
+          <t>18,32; 19,41</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>17,57; 18,3</t>
+          <t>17,62; 18,43</t>
         </is>
       </c>
     </row>
@@ -1068,42 +1068,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>19,78</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>19,95</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>19,11</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>19,41</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>19,01</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>19,29</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>18,82</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>18,96</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>19,78</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>19,95</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>19,11</t>
-        </is>
-      </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>19,3</t>
+          <t>18,8</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1123,7 +1123,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>19,14</t>
+          <t>19,12</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1136,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>18,72; 19,28</t>
+          <t>19,45; 20,22</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>18,97; 19,64</t>
+          <t>19,58; 20,55</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>18,53; 19,14</t>
+          <t>18,8; 19,51</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>18,56; 19,67</t>
+          <t>19,06; 19,89</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>19,46; 20,24</t>
+          <t>18,75; 19,3</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>19,56; 20,54</t>
+          <t>18,99; 19,62</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>18,75; 19,46</t>
+          <t>18,55; 19,16</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>18,94; 19,78</t>
+          <t>18,47; 19,17</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>19,18; 19,66</t>
+          <t>19,18; 19,68</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>19,38; 19,97</t>
+          <t>19,37; 19,95</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>18,73; 19,21</t>
+          <t>18,73; 19,2</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>18,89; 19,55</t>
+          <t>18,87; 19,44</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/imc_inf-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/imc_inf-Estudios-trans_orig.xlsx
@@ -16,7 +16,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.##"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -125,7 +127,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -138,6 +140,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -504,7 +509,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N12"/>
+  <dimension ref="A1:N16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -526,7 +531,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Índice de masa corporal (IMC) medio de los menores, declarado por los/as progenitores/as (tasa de respuesta: 87,47%)</t>
+          <t>Índice de masa corporal (IMC) medio de los menores, declarado por madres/padres (tasa de respuesta: 79,86%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -646,419 +651,271 @@
           <t>Media</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>20,87</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>19,83</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>19,88</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>19,98</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>19,26</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>19,62</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>21,14</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>19,67</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>20,01</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>19,72</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>20,47</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>19,84</t>
-        </is>
+      <c r="C4" s="5" t="n">
+        <v>20.86529349865357</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>19.83348147441913</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>19.87781866720399</v>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>19.98168359523008</v>
+      </c>
+      <c r="G4" s="5" t="n">
+        <v>19.26333024665388</v>
+      </c>
+      <c r="H4" s="5" t="n">
+        <v>19.62265913146344</v>
+      </c>
+      <c r="I4" s="5" t="n">
+        <v>21.14193403490406</v>
+      </c>
+      <c r="J4" s="5" t="n">
+        <v>19.66534697145584</v>
+      </c>
+      <c r="K4" s="5" t="n">
+        <v>20.00682354934691</v>
+      </c>
+      <c r="L4" s="5" t="n">
+        <v>19.72394945849364</v>
+      </c>
+      <c r="M4" s="5" t="n">
+        <v>20.46568489873317</v>
+      </c>
+      <c r="N4" s="5" t="n">
+        <v>19.83879443072684</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>19,79; 23,13</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>19,05; 20,58</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>18,94; 21,02</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>18,56; 24,98</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>18,44; 20,24</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>18,69; 20,58</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>19,8; 23,04</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>18,73; 20,69</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>19,35; 21,3</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>19,18; 20,37</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>19,61; 21,51</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>18,94; 21,71</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>19.79025951895707</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>19.05140179106103</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>18.93951020772705</v>
+      </c>
+      <c r="F5" s="5" t="n">
+        <v>18.55864236024997</v>
+      </c>
+      <c r="G5" s="5" t="n">
+        <v>18.44156232332557</v>
+      </c>
+      <c r="H5" s="5" t="n">
+        <v>18.68757185505833</v>
+      </c>
+      <c r="I5" s="5" t="n">
+        <v>19.79620506948516</v>
+      </c>
+      <c r="J5" s="5" t="n">
+        <v>18.72527341110931</v>
+      </c>
+      <c r="K5" s="5" t="n">
+        <v>19.35347092832308</v>
+      </c>
+      <c r="L5" s="5" t="n">
+        <v>19.17870660184559</v>
+      </c>
+      <c r="M5" s="5" t="n">
+        <v>19.61083252497157</v>
+      </c>
+      <c r="N5" s="5" t="n">
+        <v>18.9376493369913</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>23.13199256919366</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>20.58394865335049</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>21.01936104663717</v>
+      </c>
+      <c r="F6" s="5" t="n">
+        <v>24.98235876099795</v>
+      </c>
+      <c r="G6" s="5" t="n">
+        <v>20.24413674070668</v>
+      </c>
+      <c r="H6" s="5" t="n">
+        <v>20.57977481412613</v>
+      </c>
+      <c r="I6" s="5" t="n">
+        <v>23.03634027805771</v>
+      </c>
+      <c r="J6" s="5" t="n">
+        <v>20.69187625027219</v>
+      </c>
+      <c r="K6" s="5" t="n">
+        <v>21.29709529341548</v>
+      </c>
+      <c r="L6" s="5" t="n">
+        <v>20.37491767394398</v>
+      </c>
+      <c r="M6" s="5" t="n">
+        <v>21.51098867351439</v>
+      </c>
+      <c r="N6" s="5" t="n">
+        <v>21.71257154716998</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
         <is>
           <t>Secundarios</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>Media</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>19,69</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>20,33</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>19,09</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>19,83</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>19,14</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>19,47</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>18,59</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>19,01</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>19,43</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>19,91</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>18,85</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>19,45</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>19,34; 20,09</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>19,8; 21,16</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>18,68; 19,54</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>19,43; 20,42</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>18,8; 19,5</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>19,05; 19,86</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>18,27; 18,92</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>18,63; 19,5</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>19,17; 19,69</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>19,54; 20,38</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>18,61; 19,13</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>19,13; 19,82</t>
-        </is>
+      <c r="C7" s="5" t="n">
+        <v>19.68773674419465</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>20.32724220705234</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>19.0866259637227</v>
+      </c>
+      <c r="F7" s="5" t="n">
+        <v>19.83493718624075</v>
+      </c>
+      <c r="G7" s="5" t="n">
+        <v>19.13889214945134</v>
+      </c>
+      <c r="H7" s="5" t="n">
+        <v>19.46517821407239</v>
+      </c>
+      <c r="I7" s="5" t="n">
+        <v>18.59061698404932</v>
+      </c>
+      <c r="J7" s="5" t="n">
+        <v>19.00516914748881</v>
+      </c>
+      <c r="K7" s="5" t="n">
+        <v>19.43417569060015</v>
+      </c>
+      <c r="L7" s="5" t="n">
+        <v>19.91178253749799</v>
+      </c>
+      <c r="M7" s="5" t="n">
+        <v>18.84612930876107</v>
+      </c>
+      <c r="N7" s="5" t="n">
+        <v>19.44639266033496</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>Universitarios</t>
-        </is>
-      </c>
+      <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Media</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>19,51</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>18,97</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>18,86</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>17,91</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>18,56</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>18,61</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>18,65</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>18,0</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>19,0</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>18,8</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>18,76</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>17,95</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>19.33576042421643</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>19.79503817619792</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>18.68441976981689</v>
+      </c>
+      <c r="F8" s="5" t="n">
+        <v>19.43372548474267</v>
+      </c>
+      <c r="G8" s="5" t="n">
+        <v>18.80213678811745</v>
+      </c>
+      <c r="H8" s="5" t="n">
+        <v>19.04827325614887</v>
+      </c>
+      <c r="I8" s="5" t="n">
+        <v>18.27355860347373</v>
+      </c>
+      <c r="J8" s="5" t="n">
+        <v>18.62802800974796</v>
+      </c>
+      <c r="K8" s="5" t="n">
+        <v>19.17322820106764</v>
+      </c>
+      <c r="L8" s="5" t="n">
+        <v>19.54395538507992</v>
+      </c>
+      <c r="M8" s="5" t="n">
+        <v>18.60840676901186</v>
+      </c>
+      <c r="N8" s="5" t="n">
+        <v>19.1304515838013</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>18,69; 20,98</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>18,43; 19,63</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>18,21; 19,74</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>17,48; 18,38</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>18,1; 19,19</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>18,01; 19,25</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>18,03; 19,56</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>17,42; 18,73</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>18,47; 19,73</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>18,41; 19,23</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>18,32; 19,41</t>
-        </is>
-      </c>
-      <c r="N9" s="2" t="inlineStr">
-        <is>
-          <t>17,62; 18,43</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>20.08660010559374</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>21.16038446915416</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>19.54032879007245</v>
+      </c>
+      <c r="F9" s="5" t="n">
+        <v>20.42237624867179</v>
+      </c>
+      <c r="G9" s="5" t="n">
+        <v>19.50248048284369</v>
+      </c>
+      <c r="H9" s="5" t="n">
+        <v>19.86386973847543</v>
+      </c>
+      <c r="I9" s="5" t="n">
+        <v>18.920299842788</v>
+      </c>
+      <c r="J9" s="5" t="n">
+        <v>19.4955169184524</v>
+      </c>
+      <c r="K9" s="5" t="n">
+        <v>19.69242021583939</v>
+      </c>
+      <c r="L9" s="5" t="n">
+        <v>20.37790581735695</v>
+      </c>
+      <c r="M9" s="5" t="n">
+        <v>19.12869245210219</v>
+      </c>
+      <c r="N9" s="5" t="n">
+        <v>19.81675610190492</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Universitarios</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -1066,137 +923,269 @@
           <t>Media</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>19,78</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>19,95</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>19,11</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>19,41</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>19,01</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>19,29</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>18,82</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>18,8</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>19,41</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>19,63</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>18,97</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>19,12</t>
-        </is>
+      <c r="C10" s="5" t="n">
+        <v>19.50778783596166</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>18.97298221572936</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>18.86289411612011</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>17.91278555094173</v>
+      </c>
+      <c r="G10" s="5" t="n">
+        <v>18.55835323197239</v>
+      </c>
+      <c r="H10" s="5" t="n">
+        <v>18.60597812510764</v>
+      </c>
+      <c r="I10" s="5" t="n">
+        <v>18.65272707404937</v>
+      </c>
+      <c r="J10" s="5" t="n">
+        <v>17.99719367741334</v>
+      </c>
+      <c r="K10" s="5" t="n">
+        <v>18.9984593779211</v>
+      </c>
+      <c r="L10" s="5" t="n">
+        <v>18.79580981608046</v>
+      </c>
+      <c r="M10" s="5" t="n">
+        <v>18.7615417524729</v>
+      </c>
+      <c r="N10" s="5" t="n">
+        <v>17.95433456490455</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>19,45; 20,22</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>19,58; 20,55</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>18,8; 19,51</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>19,06; 19,89</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>18,75; 19,3</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>18,99; 19,62</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>18,55; 19,16</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>18,47; 19,17</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>19,18; 19,68</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>19,37; 19,95</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>18,73; 19,2</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>18,87; 19,44</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>18.69300174242182</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>18.43041876552392</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>18.2136831570298</v>
+      </c>
+      <c r="F11" s="5" t="n">
+        <v>17.47815338926532</v>
+      </c>
+      <c r="G11" s="5" t="n">
+        <v>18.09869943815415</v>
+      </c>
+      <c r="H11" s="5" t="n">
+        <v>18.01339727937078</v>
+      </c>
+      <c r="I11" s="5" t="n">
+        <v>18.03157274035159</v>
+      </c>
+      <c r="J11" s="5" t="n">
+        <v>17.41930907464936</v>
+      </c>
+      <c r="K11" s="5" t="n">
+        <v>18.46578455814608</v>
+      </c>
+      <c r="L11" s="5" t="n">
+        <v>18.40693047177803</v>
+      </c>
+      <c r="M11" s="5" t="n">
+        <v>18.32216831495657</v>
+      </c>
+      <c r="N11" s="5" t="n">
+        <v>17.62198908668714</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>20.97998241808428</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>19.62574986930112</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>19.73646181866883</v>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>18.38357695931143</v>
+      </c>
+      <c r="G12" s="5" t="n">
+        <v>19.19190674423387</v>
+      </c>
+      <c r="H12" s="5" t="n">
+        <v>19.25336503427633</v>
+      </c>
+      <c r="I12" s="5" t="n">
+        <v>19.55929299983989</v>
+      </c>
+      <c r="J12" s="5" t="n">
+        <v>18.73092301102023</v>
+      </c>
+      <c r="K12" s="5" t="n">
+        <v>19.72977238947682</v>
+      </c>
+      <c r="L12" s="5" t="n">
+        <v>19.23107109664991</v>
+      </c>
+      <c r="M12" s="5" t="n">
+        <v>19.40799304166732</v>
+      </c>
+      <c r="N12" s="5" t="n">
+        <v>18.4297274912158</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>19.7837111511778</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>19.9531945933317</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>19.10766551521962</v>
+      </c>
+      <c r="F13" s="5" t="n">
+        <v>19.40675793458474</v>
+      </c>
+      <c r="G13" s="5" t="n">
+        <v>19.00870532088818</v>
+      </c>
+      <c r="H13" s="5" t="n">
+        <v>19.2863330261248</v>
+      </c>
+      <c r="I13" s="5" t="n">
+        <v>18.82493221474763</v>
+      </c>
+      <c r="J13" s="5" t="n">
+        <v>18.80406017074265</v>
+      </c>
+      <c r="K13" s="5" t="n">
+        <v>19.40517326971147</v>
+      </c>
+      <c r="L13" s="5" t="n">
+        <v>19.62867365837565</v>
+      </c>
+      <c r="M13" s="5" t="n">
+        <v>18.97125170427613</v>
+      </c>
+      <c r="N13" s="5" t="n">
+        <v>19.12187026395803</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>19.44555463527815</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>19.58389989119731</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>18.80035537625711</v>
+      </c>
+      <c r="F14" s="5" t="n">
+        <v>19.06347902053687</v>
+      </c>
+      <c r="G14" s="5" t="n">
+        <v>18.74685702743109</v>
+      </c>
+      <c r="H14" s="5" t="n">
+        <v>18.98891526856099</v>
+      </c>
+      <c r="I14" s="5" t="n">
+        <v>18.55349939543848</v>
+      </c>
+      <c r="J14" s="5" t="n">
+        <v>18.46970846249161</v>
+      </c>
+      <c r="K14" s="5" t="n">
+        <v>19.17947951219681</v>
+      </c>
+      <c r="L14" s="5" t="n">
+        <v>19.37085113078464</v>
+      </c>
+      <c r="M14" s="5" t="n">
+        <v>18.72806457421745</v>
+      </c>
+      <c r="N14" s="5" t="n">
+        <v>18.86739973730429</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>20.22230863420729</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>20.5494973936245</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>19.50517297894157</v>
+      </c>
+      <c r="F15" s="5" t="n">
+        <v>19.88734830565901</v>
+      </c>
+      <c r="G15" s="5" t="n">
+        <v>19.2959412618326</v>
+      </c>
+      <c r="H15" s="5" t="n">
+        <v>19.61634376037163</v>
+      </c>
+      <c r="I15" s="5" t="n">
+        <v>19.16249397821689</v>
+      </c>
+      <c r="J15" s="5" t="n">
+        <v>19.17022272898184</v>
+      </c>
+      <c r="K15" s="5" t="n">
+        <v>19.67735933811362</v>
+      </c>
+      <c r="L15" s="5" t="n">
+        <v>19.95436453746586</v>
+      </c>
+      <c r="M15" s="5" t="n">
+        <v>19.19865690315783</v>
+      </c>
+      <c r="N15" s="5" t="n">
+        <v>19.44411036641491</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
         </is>
@@ -1204,14 +1193,14 @@
     </row>
   </sheetData>
   <mergeCells count="8">
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A10:A12"/>
     <mergeCell ref="A1:B2"/>
     <mergeCell ref="C1:F1"/>
     <mergeCell ref="G1:J1"/>
-    <mergeCell ref="A6:A7"/>
     <mergeCell ref="K1:N1"/>
+    <mergeCell ref="A13:A15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/trans_orig/imc_inf-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/imc_inf-Estudios-trans_orig.xlsx
@@ -531,7 +531,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Índice de masa corporal (IMC) medio de los menores, declarado por madres/padres (tasa de respuesta: 79,86%)</t>
+          <t>Índice de masa corporal (IMC) medio de los menores, declarado por madres/padres (tasa de respuesta: 87,47%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
